--- a/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -768,47 +768,54 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>The 'Otros' flows are what is left of each zone's pipeline import after distributor billing, so they absorb billing-cycle timing and can be noisy month to month.</t>
+          <t>The 'Otros' flows are each zone's pipeline import less the distributor's metered intake.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Tariff flows are BILLED volumes (meter-reading cycles lag physical flow, so a distributor's billing can be well above or below its intake in the shoulder months). Residential / Commercial / large-user volumes here are each distributor's metered intake split pro rata to that month's billing; the billed volumes as published are in 'Flows by tariff (m3)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Total: sum of sectors. Imports: Gasoducto del Litoral + Gasoducto Cruz del Sur (should match Total).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Monthly from 2021-01. Uruguay has no domestic production; all gas is imported from Argentina. The last 3 months are re-fetched on every run (billing revisions); a month is added once all three distributors report.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MIEM / DNE (Planificacion, Estadistica y Balance), VisualPEB gas natural - 'Flujos de gas natural segun Tarifas' (monthly): https://visualpeb.miem.gub.uy/visualPEB/gas_natural</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>MIEM / DNE (Planificacion, Estadistica y Balance), VisualPEB gas natural - 'Flujos de gas natural segun Tarifas' (monthly): https://visualpeb.miem.gub.uy/visualPEB/gas_natural</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Underlying series (downloadable zip): https://www.gub.uy/ministerio-industria-energia-mineria/datos-y-estadisticas/datos/series-estadisticas-gas-natural</t>
         </is>
@@ -868,13 +875,16 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0165</v>
+        <v>0.0157</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0343</v>
+        <v>0.0326</v>
       </c>
       <c r="D2" t="n">
         <v>0.0327</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0774</v>
@@ -885,13 +895,13 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0148</v>
+        <v>0.0163</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0377</v>
+        <v>0.0411</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0218</v>
+        <v>0.0227</v>
       </c>
       <c r="E3" t="n">
         <v>0.0605</v>
@@ -905,13 +915,16 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0157</v>
+        <v>0.0178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0403</v>
+        <v>0.0451</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0299</v>
+        <v>0.0311</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0.063</v>
@@ -922,13 +935,13 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0229</v>
+        <v>0.0208</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0535</v>
+        <v>0.0488</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0284</v>
+        <v>0.0271</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -942,13 +955,13 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0494</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0545</v>
+        <v>0.0893</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0289</v>
+        <v>0.0392</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -962,13 +975,13 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1469</v>
+        <v>0.1613</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0767</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0234</v>
+        <v>0.0246</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -982,13 +995,16 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1643</v>
+        <v>0.1797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0746</v>
+        <v>0.0801</v>
       </c>
       <c r="D8" t="n">
-        <v>0.029</v>
+        <v>0.0306</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0075</v>
@@ -999,13 +1015,16 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1782</v>
+        <v>0.1698</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0809</v>
+        <v>0.0772</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0286</v>
+        <v>0.0278</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0104</v>
@@ -1016,13 +1035,13 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1444</v>
+        <v>0.1252</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0267</v>
+        <v>0.0245</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1036,13 +1055,16 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0721</v>
+        <v>0.0571</v>
       </c>
       <c r="D11" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0.1224</v>
@@ -1053,13 +1075,16 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0349</v>
+        <v>0.0304</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0598</v>
+        <v>0.0526</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0282</v>
+        <v>0.0261</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0.1121</v>
@@ -1070,13 +1095,16 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0189</v>
+        <v>0.0181</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0547</v>
+        <v>0.052</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0242</v>
+        <v>0.0238</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0945</v>
@@ -1087,13 +1115,16 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0153</v>
+        <v>0.0144</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0491</v>
+        <v>0.046</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0239</v>
+        <v>0.0244</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0.06419999999999999</v>
@@ -1104,13 +1135,16 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0141</v>
+        <v>0.0146</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0466</v>
+        <v>0.0483</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0288</v>
+        <v>0.029</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0593</v>
@@ -1121,13 +1155,16 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0187</v>
+        <v>0.0193</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0586</v>
+        <v>0.0602</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0319</v>
+        <v>0.032</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0711</v>
@@ -1138,13 +1175,16 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0222</v>
+        <v>0.0241</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0574</v>
+        <v>0.0621</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0263</v>
+        <v>0.0283</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0618</v>
@@ -1155,13 +1195,16 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0618</v>
+        <v>0.0922</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0983</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0212</v>
+        <v>0.0287</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0.06710000000000001</v>
@@ -1172,13 +1215,16 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1689</v>
+        <v>0.1864</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0897</v>
+        <v>0.0977</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0218</v>
+        <v>0.0237</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0098</v>
@@ -1189,13 +1235,16 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1734</v>
+        <v>0.1704</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0828</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0201</v>
+        <v>0.02</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0.004</v>
@@ -1206,13 +1255,16 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1543</v>
+        <v>0.1514</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0803</v>
+        <v>0.0789</v>
       </c>
       <c r="D21" t="n">
-        <v>0.029</v>
+        <v>0.0287</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0377</v>
@@ -1223,13 +1275,16 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1346</v>
+        <v>0.1093</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0304</v>
+        <v>0.028</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0825</v>
@@ -1240,13 +1295,16 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0847</v>
+        <v>0.0735</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0653</v>
+        <v>0.0578</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0275</v>
+        <v>0.0264</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0.1399</v>
@@ -1257,13 +1315,16 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0435</v>
+        <v>0.0345</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0568</v>
+        <v>0.0459</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0261</v>
+        <v>0.0222</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0.1333</v>
@@ -1274,13 +1335,16 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0172</v>
+        <v>0.0157</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0485</v>
+        <v>0.0445</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0229</v>
+        <v>0.0218</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0.1059</v>
@@ -1291,13 +1355,16 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0128</v>
+        <v>0.012</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0426</v>
+        <v>0.0399</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0183</v>
+        <v>0.0178</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0.08939999999999999</v>
@@ -1308,13 +1375,16 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0426</v>
+        <v>0.0429</v>
       </c>
       <c r="D27" t="n">
-        <v>0.024</v>
+        <v>0.0243</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0.056</v>
@@ -1325,13 +1395,16 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>0.014</v>
+        <v>0.0146</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0496</v>
+        <v>0.0516</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0326</v>
+        <v>0.0335</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0728</v>
@@ -1342,13 +1415,16 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0216</v>
+        <v>0.0221</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0556</v>
+        <v>0.057</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0322</v>
+        <v>0.0335</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0949</v>
@@ -1359,13 +1435,16 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0383</v>
+        <v>0.0505</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0567</v>
+        <v>0.0727</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0188</v>
+        <v>0.0231</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0.08459999999999999</v>
@@ -1376,13 +1455,16 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1039</v>
+        <v>0.1179</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0796</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0204</v>
+        <v>0.0224</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0.1086</v>
@@ -1393,13 +1475,16 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1229</v>
+        <v>0.1348</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0688</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.018</v>
+        <v>0.0196</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0.11</v>
@@ -1410,13 +1495,16 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1265</v>
+        <v>0.1302</v>
       </c>
       <c r="C33" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0212</v>
+        <v>0.0216</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0.096</v>
@@ -1427,13 +1515,16 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1366</v>
+        <v>0.1222</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0722</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0235</v>
+        <v>0.0221</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0506</v>
@@ -1444,13 +1535,16 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0895</v>
+        <v>0.073</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0609</v>
+        <v>0.0506</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0359</v>
+        <v>0.0324</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0319</v>
@@ -1461,13 +1555,16 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0499</v>
+        <v>0.0408</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0605</v>
+        <v>0.0503</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0356</v>
+        <v>0.032</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0.02</v>
@@ -1478,13 +1575,19 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0187</v>
+        <v>0.0184</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0497</v>
+        <v>0.0489</v>
       </c>
       <c r="D37" t="n">
         <v>0.035</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1492,13 +1595,19 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0135</v>
+        <v>0.0126</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0456</v>
+        <v>0.0423</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0354</v>
+        <v>0.0333</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1506,13 +1615,16 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0124</v>
+        <v>0.0122</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0457</v>
+        <v>0.0449</v>
       </c>
       <c r="D39" t="n">
         <v>0.025</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1523,13 +1635,16 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>0.012</v>
+        <v>0.0149</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0402</v>
+        <v>0.0495</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0268</v>
+        <v>0.0324</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0473</v>
@@ -1540,13 +1655,16 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0199</v>
+        <v>0.02</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0625</v>
+        <v>0.0626</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0461</v>
+        <v>0.046</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0.08690000000000001</v>
@@ -1557,13 +1675,16 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0704</v>
+        <v>0.098</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0743</v>
+        <v>0.1004</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0284</v>
+        <v>0.0342</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0.1476</v>
@@ -1574,13 +1695,16 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1208</v>
+        <v>0.1186</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0793</v>
+        <v>0.0785</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0195</v>
+        <v>0.0197</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0.142</v>
@@ -1591,13 +1715,16 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1411</v>
+        <v>0.1611</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0798</v>
+        <v>0.0891</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0172</v>
+        <v>0.0191</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0.0617</v>
@@ -1608,13 +1735,16 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1471</v>
+        <v>0.1483</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0746</v>
+        <v>0.0751</v>
       </c>
       <c r="D45" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0.06909999999999999</v>
@@ -1625,13 +1755,16 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1313</v>
+        <v>0.0963</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0558</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0307</v>
+        <v>0.0254</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0.0721</v>
@@ -1642,13 +1775,16 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>0.056</v>
+        <v>0.0451</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0589</v>
+        <v>0.0486</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0463</v>
+        <v>0.0397</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0.0906</v>
@@ -1659,13 +1795,16 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0247</v>
+        <v>0.022</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0533</v>
+        <v>0.0476</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0388</v>
+        <v>0.0362</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0.0609</v>
@@ -1676,13 +1815,16 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0477</v>
+        <v>0.0478</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0303</v>
+        <v>0.0308</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0.0297</v>
@@ -1693,13 +1835,16 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0138</v>
+        <v>0.0125</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0451</v>
+        <v>0.0407</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0345</v>
+        <v>0.0319</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0.0185</v>
@@ -1710,13 +1855,16 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>0.0124</v>
+        <v>0.0116</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0468</v>
+        <v>0.044</v>
       </c>
       <c r="D51" t="n">
         <v>0.0198</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0.0409</v>
@@ -1727,13 +1875,16 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0133</v>
+        <v>0.0145</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0474</v>
+        <v>0.0517</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0266</v>
+        <v>0.0288</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0.0339</v>
@@ -1744,13 +1895,16 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0177</v>
+        <v>0.0195</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0523</v>
+        <v>0.0574</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0285</v>
+        <v>0.0314</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0.0473</v>
@@ -1761,13 +1915,16 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0365</v>
+        <v>0.0463</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0653</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0279</v>
+        <v>0.0321</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0.0834</v>
@@ -1778,13 +1935,16 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1106</v>
+        <v>0.1389</v>
       </c>
       <c r="C55" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0969</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0344</v>
+        <v>0.0406</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0.095</v>
@@ -1795,13 +1955,16 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>0.156</v>
+        <v>0.1609</v>
       </c>
       <c r="C56" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0825</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0341</v>
+        <v>0.0344</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0.1234</v>
@@ -1812,13 +1975,13 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1412</v>
+        <v>0.1306</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0333</v>
+        <v>0.0315</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -1832,13 +1995,13 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1124</v>
+        <v>0.1034</v>
       </c>
       <c r="C58" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0315</v>
+        <v>0.0295</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -1852,13 +2015,13 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0616</v>
+        <v>0.0469</v>
       </c>
       <c r="C59" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0522</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0325</v>
+        <v>0.0272</v>
       </c>
       <c r="E59" t="n">
         <v>0.0009</v>
@@ -1872,13 +2035,13 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>0.0338</v>
+        <v>0.0294</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0616</v>
+        <v>0.0543</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0379</v>
+        <v>0.0349</v>
       </c>
       <c r="E60" t="n">
         <v>0.0013</v>
@@ -1892,13 +2055,13 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0157</v>
+        <v>0.0148</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0477</v>
+        <v>0.045</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0397</v>
+        <v>0.038</v>
       </c>
       <c r="E61" t="n">
         <v>0.2925</v>
@@ -1912,13 +2075,13 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0133</v>
+        <v>0.0131</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0478</v>
+        <v>0.0469</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0316</v>
+        <v>0.0315</v>
       </c>
       <c r="E62" t="n">
         <v>0.2702</v>
@@ -1932,13 +2095,13 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0152</v>
+        <v>0.0129</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0505</v>
+        <v>0.0431</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0406</v>
+        <v>0.0353</v>
       </c>
       <c r="E63" t="n">
         <v>0.5302</v>
@@ -1952,13 +2115,13 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0103</v>
+        <v>0.0114</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0523</v>
+        <v>0.0579</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0321</v>
+        <v>0.0354</v>
       </c>
       <c r="E64" t="n">
         <v>0.7425</v>
@@ -1972,13 +2135,13 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0191</v>
+        <v>0.0199</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0599</v>
+        <v>0.0621</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0412</v>
+        <v>0.0423</v>
       </c>
       <c r="E65" t="n">
         <v>0.2324</v>
@@ -1992,13 +2155,13 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0818</v>
+        <v>0.1107</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0452</v>
+        <v>0.0558</v>
       </c>
       <c r="E66" t="n">
         <v>0.0092</v>
@@ -2012,13 +2175,13 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1318</v>
+        <v>0.1433</v>
       </c>
       <c r="C67" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0921</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0517</v>
+        <v>0.0541</v>
       </c>
       <c r="E67" t="n">
         <v>0.0726</v>
@@ -2126,37 +2289,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.511</v>
+        <v>0.485</v>
       </c>
       <c r="C2" t="n">
-        <v>1.062</v>
+        <v>1.012</v>
       </c>
       <c r="D2" t="n">
-        <v>1.015</v>
+        <v>1.014</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.988</v>
+        <v>4.911</v>
       </c>
       <c r="H2" t="n">
         <v>4.911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0165</v>
+        <v>0.0157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0343</v>
+        <v>0.0326</v>
       </c>
       <c r="K2" t="n">
         <v>0.0327</v>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="n">
         <v>0.0774</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1609</v>
+        <v>0.1584</v>
       </c>
       <c r="O2" t="n">
         <v>0.1584</v>
@@ -2169,13 +2338,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.414</v>
+        <v>0.457</v>
       </c>
       <c r="C3" t="n">
-        <v>1.056</v>
+        <v>1.15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.61</v>
+        <v>0.636</v>
       </c>
       <c r="E3" t="n">
         <v>1.694</v>
@@ -2184,19 +2353,19 @@
         <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>5.383</v>
+        <v>5.547</v>
       </c>
       <c r="H3" t="n">
         <v>5.547</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0148</v>
+        <v>0.0163</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0377</v>
+        <v>0.0411</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0218</v>
+        <v>0.0227</v>
       </c>
       <c r="L3" t="n">
         <v>0.0605</v>
@@ -2205,7 +2374,7 @@
         <v>0.0575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1922</v>
+        <v>0.1981</v>
       </c>
       <c r="O3" t="n">
         <v>0.1981</v>
@@ -2218,37 +2387,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.488</v>
+        <v>0.551</v>
       </c>
       <c r="C4" t="n">
-        <v>1.248</v>
+        <v>1.397</v>
       </c>
       <c r="D4" t="n">
-        <v>0.927</v>
+        <v>0.963</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1.953</v>
       </c>
       <c r="G4" t="n">
-        <v>4.616</v>
+        <v>4.863</v>
       </c>
       <c r="H4" t="n">
         <v>4.863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0157</v>
+        <v>0.0178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0403</v>
+        <v>0.0451</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0299</v>
+        <v>0.0311</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0.063</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1489</v>
+        <v>0.1569</v>
       </c>
       <c r="O4" t="n">
         <v>0.1569</v>
@@ -2261,13 +2436,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.623</v>
       </c>
       <c r="C5" t="n">
-        <v>1.606</v>
+        <v>1.463</v>
       </c>
       <c r="D5" t="n">
-        <v>0.851</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2276,19 +2451,19 @@
         <v>2.437</v>
       </c>
       <c r="G5" t="n">
-        <v>5.582</v>
+        <v>5.337</v>
       </c>
       <c r="H5" t="n">
         <v>5.337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0229</v>
+        <v>0.0208</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0535</v>
+        <v>0.0488</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0284</v>
+        <v>0.0271</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2297,7 +2472,7 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1861</v>
+        <v>0.1779</v>
       </c>
       <c r="O5" t="n">
         <v>0.1779</v>
@@ -2310,13 +2485,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.533</v>
+        <v>2.603</v>
       </c>
       <c r="C6" t="n">
-        <v>1.69</v>
+        <v>2.767</v>
       </c>
       <c r="D6" t="n">
-        <v>0.895</v>
+        <v>1.214</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2325,19 +2500,19 @@
         <v>0.619</v>
       </c>
       <c r="G6" t="n">
-        <v>4.736</v>
+        <v>7.204</v>
       </c>
       <c r="H6" t="n">
         <v>7.204</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0494</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0545</v>
+        <v>0.0893</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0289</v>
+        <v>0.0392</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2346,7 +2521,7 @@
         <v>0.02</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1528</v>
+        <v>0.2324</v>
       </c>
       <c r="O6" t="n">
         <v>0.2324</v>
@@ -2359,13 +2534,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.407</v>
+        <v>4.839</v>
       </c>
       <c r="C7" t="n">
-        <v>2.301</v>
+        <v>2.509</v>
       </c>
       <c r="D7" t="n">
-        <v>0.702</v>
+        <v>0.739</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2374,19 +2549,19 @@
         <v>0.168</v>
       </c>
       <c r="G7" t="n">
-        <v>7.578</v>
+        <v>8.254</v>
       </c>
       <c r="H7" t="n">
         <v>8.254</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1469</v>
+        <v>0.1613</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0767</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0234</v>
+        <v>0.0246</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2395,7 +2570,7 @@
         <v>0.0056</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2526</v>
+        <v>0.2751</v>
       </c>
       <c r="O7" t="n">
         <v>0.2751</v>
@@ -2408,37 +2583,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.093</v>
+        <v>5.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2.313</v>
+        <v>2.483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0.233</v>
       </c>
       <c r="G8" t="n">
-        <v>8.539</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>9.234999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1643</v>
+        <v>0.1797</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0746</v>
+        <v>0.0801</v>
       </c>
       <c r="K8" t="n">
-        <v>0.029</v>
+        <v>0.0306</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0.0075</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2754</v>
+        <v>0.2979</v>
       </c>
       <c r="O8" t="n">
         <v>0.2979</v>
@@ -2451,37 +2632,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.525</v>
+        <v>5.265</v>
       </c>
       <c r="C9" t="n">
-        <v>2.507</v>
+        <v>2.394</v>
       </c>
       <c r="D9" t="n">
-        <v>0.887</v>
+        <v>0.863</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0.324</v>
       </c>
       <c r="G9" t="n">
-        <v>9.243</v>
+        <v>8.845000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>8.845000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1782</v>
+        <v>0.1698</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0809</v>
+        <v>0.0772</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0286</v>
+        <v>0.0278</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0.0104</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2982</v>
+        <v>0.2853</v>
       </c>
       <c r="O9" t="n">
         <v>0.2853</v>
@@ -2494,13 +2681,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.331</v>
+        <v>3.756</v>
       </c>
       <c r="C10" t="n">
-        <v>2.362</v>
+        <v>2.062</v>
       </c>
       <c r="D10" t="n">
-        <v>0.801</v>
+        <v>0.734</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2509,19 +2696,19 @@
         <v>0.474</v>
       </c>
       <c r="G10" t="n">
-        <v>7.968</v>
+        <v>7.027</v>
       </c>
       <c r="H10" t="n">
         <v>7.027</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1444</v>
+        <v>0.1252</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0267</v>
+        <v>0.0245</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2530,7 +2717,7 @@
         <v>0.0158</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2656</v>
+        <v>0.2342</v>
       </c>
       <c r="O10" t="n">
         <v>0.2342</v>
@@ -2543,37 +2730,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.981</v>
+        <v>2.255</v>
       </c>
       <c r="C11" t="n">
-        <v>2.237</v>
+        <v>1.771</v>
       </c>
       <c r="D11" t="n">
-        <v>0.992</v>
+        <v>0.931</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>3.795</v>
       </c>
       <c r="G11" t="n">
-        <v>10.004</v>
+        <v>8.750999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>8.750999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0721</v>
+        <v>0.0571</v>
       </c>
       <c r="K11" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0.1224</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3227</v>
+        <v>0.2823</v>
       </c>
       <c r="O11" t="n">
         <v>0.2823</v>
@@ -2586,37 +2779,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.046</v>
+        <v>0.912</v>
       </c>
       <c r="C12" t="n">
-        <v>1.795</v>
+        <v>1.577</v>
       </c>
       <c r="D12" t="n">
-        <v>0.847</v>
+        <v>0.784</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>3.364</v>
       </c>
       <c r="G12" t="n">
-        <v>7.052</v>
+        <v>6.638</v>
       </c>
       <c r="H12" t="n">
         <v>6.638</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0349</v>
+        <v>0.0304</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0598</v>
+        <v>0.0526</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0282</v>
+        <v>0.0261</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0.1121</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2351</v>
+        <v>0.2213</v>
       </c>
       <c r="O12" t="n">
         <v>0.2213</v>
@@ -2629,37 +2828,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.587</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>1.696</v>
+        <v>1.611</v>
       </c>
       <c r="D13" t="n">
-        <v>0.751</v>
+        <v>0.738</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>2.929</v>
       </c>
       <c r="G13" t="n">
-        <v>5.964</v>
+        <v>5.839</v>
       </c>
       <c r="H13" t="n">
         <v>5.839</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0189</v>
+        <v>0.0181</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0547</v>
+        <v>0.052</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0242</v>
+        <v>0.0238</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0.0945</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1924</v>
+        <v>0.1883</v>
       </c>
       <c r="O13" t="n">
         <v>0.1883</v>
@@ -2672,37 +2877,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.475</v>
+        <v>0.447</v>
       </c>
       <c r="C14" t="n">
-        <v>1.521</v>
+        <v>1.426</v>
       </c>
       <c r="D14" t="n">
-        <v>0.741</v>
+        <v>0.755</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.989</v>
       </c>
       <c r="G14" t="n">
-        <v>4.726</v>
+        <v>4.617</v>
       </c>
       <c r="H14" t="n">
         <v>4.617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0153</v>
+        <v>0.0144</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0491</v>
+        <v>0.046</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0239</v>
+        <v>0.0244</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0.06419999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1524</v>
+        <v>0.1489</v>
       </c>
       <c r="O14" t="n">
         <v>0.1489</v>
@@ -2715,37 +2926,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.394</v>
+        <v>0.408</v>
       </c>
       <c r="C15" t="n">
-        <v>1.305</v>
+        <v>1.352</v>
       </c>
       <c r="D15" t="n">
-        <v>0.806</v>
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1.66</v>
       </c>
       <c r="G15" t="n">
-        <v>4.165</v>
+        <v>4.232</v>
       </c>
       <c r="H15" t="n">
         <v>4.232</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0141</v>
+        <v>0.0146</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0466</v>
+        <v>0.0483</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0288</v>
+        <v>0.029</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0.0593</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1488</v>
+        <v>0.1511</v>
       </c>
       <c r="O15" t="n">
         <v>0.1511</v>
@@ -2758,37 +2975,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.58</v>
+        <v>0.597</v>
       </c>
       <c r="C16" t="n">
-        <v>1.816</v>
+        <v>1.867</v>
       </c>
       <c r="D16" t="n">
-        <v>0.988</v>
+        <v>0.992</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>2.204</v>
       </c>
       <c r="G16" t="n">
-        <v>5.588</v>
+        <v>5.661</v>
       </c>
       <c r="H16" t="n">
         <v>5.661</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0187</v>
+        <v>0.0193</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0586</v>
+        <v>0.0602</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0319</v>
+        <v>0.032</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0.0711</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1803</v>
+        <v>0.1826</v>
       </c>
       <c r="O16" t="n">
         <v>0.1826</v>
@@ -2801,37 +3024,43 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.666</v>
+        <v>0.724</v>
       </c>
       <c r="C17" t="n">
-        <v>1.721</v>
+        <v>1.864</v>
       </c>
       <c r="D17" t="n">
-        <v>0.79</v>
+        <v>0.849</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>1.853</v>
       </c>
       <c r="G17" t="n">
-        <v>5.031</v>
+        <v>5.29</v>
       </c>
       <c r="H17" t="n">
         <v>5.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0222</v>
+        <v>0.0241</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0574</v>
+        <v>0.0621</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0263</v>
+        <v>0.0283</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0.0618</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1677</v>
+        <v>0.1763</v>
       </c>
       <c r="O17" t="n">
         <v>0.1763</v>
@@ -2844,37 +3073,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.916</v>
+        <v>2.859</v>
       </c>
       <c r="C18" t="n">
-        <v>2.094</v>
+        <v>3.046</v>
       </c>
       <c r="D18" t="n">
-        <v>0.657</v>
+        <v>0.89</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>6.747</v>
+        <v>8.875</v>
       </c>
       <c r="H18" t="n">
         <v>8.875</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0618</v>
+        <v>0.0922</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0983</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0212</v>
+        <v>0.0287</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2177</v>
+        <v>0.2863</v>
       </c>
       <c r="O18" t="n">
         <v>0.2863</v>
@@ -2887,37 +3122,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.067</v>
+        <v>5.591</v>
       </c>
       <c r="C19" t="n">
-        <v>2.691</v>
+        <v>2.932</v>
       </c>
       <c r="D19" t="n">
-        <v>0.654</v>
+        <v>0.71</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0.295</v>
       </c>
       <c r="G19" t="n">
-        <v>8.707000000000001</v>
+        <v>9.528</v>
       </c>
       <c r="H19" t="n">
         <v>9.528</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1689</v>
+        <v>0.1864</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0897</v>
+        <v>0.0977</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0218</v>
+        <v>0.0237</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0.0098</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2902</v>
+        <v>0.3176</v>
       </c>
       <c r="O19" t="n">
         <v>0.3176</v>
@@ -2930,37 +3171,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.375</v>
+        <v>5.283</v>
       </c>
       <c r="C20" t="n">
-        <v>2.566</v>
+        <v>2.53</v>
       </c>
       <c r="D20" t="n">
-        <v>0.623</v>
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0.123</v>
       </c>
       <c r="G20" t="n">
-        <v>8.686999999999999</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>8.555999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1734</v>
+        <v>0.1704</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0828</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0201</v>
+        <v>0.02</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0.004</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2802</v>
+        <v>0.276</v>
       </c>
       <c r="O20" t="n">
         <v>0.276</v>
@@ -2973,37 +3220,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.785</v>
+        <v>4.692</v>
       </c>
       <c r="C21" t="n">
-        <v>2.491</v>
+        <v>2.446</v>
       </c>
       <c r="D21" t="n">
-        <v>0.898</v>
+        <v>0.891</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>1.167</v>
       </c>
       <c r="G21" t="n">
-        <v>9.340999999999999</v>
+        <v>9.196</v>
       </c>
       <c r="H21" t="n">
         <v>9.196</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1543</v>
+        <v>0.1514</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0803</v>
+        <v>0.0789</v>
       </c>
       <c r="K21" t="n">
-        <v>0.029</v>
+        <v>0.0287</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0.0377</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3013</v>
+        <v>0.2966</v>
       </c>
       <c r="O21" t="n">
         <v>0.2966</v>
@@ -3016,37 +3269,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.037</v>
+        <v>3.28</v>
       </c>
       <c r="C22" t="n">
-        <v>2.317</v>
+        <v>1.924</v>
       </c>
       <c r="D22" t="n">
-        <v>0.911</v>
+        <v>0.839</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>2.475</v>
       </c>
       <c r="G22" t="n">
-        <v>9.739000000000001</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>8.516999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1346</v>
+        <v>0.1093</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0304</v>
+        <v>0.028</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0.0825</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3246</v>
+        <v>0.2839</v>
       </c>
       <c r="O22" t="n">
         <v>0.2839</v>
@@ -3059,37 +3318,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.627</v>
+        <v>2.28</v>
       </c>
       <c r="C23" t="n">
-        <v>2.025</v>
+        <v>1.793</v>
       </c>
       <c r="D23" t="n">
-        <v>0.854</v>
+        <v>0.819</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>4.337</v>
       </c>
       <c r="G23" t="n">
-        <v>9.843</v>
+        <v>9.228</v>
       </c>
       <c r="H23" t="n">
         <v>9.228</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0847</v>
+        <v>0.0735</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0653</v>
+        <v>0.0578</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0275</v>
+        <v>0.0264</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0.1399</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3175</v>
+        <v>0.2977</v>
       </c>
       <c r="O23" t="n">
         <v>0.2977</v>
@@ -3102,37 +3367,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.306</v>
+        <v>1.036</v>
       </c>
       <c r="C24" t="n">
-        <v>1.705</v>
+        <v>1.378</v>
       </c>
       <c r="D24" t="n">
-        <v>0.783</v>
+        <v>0.667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>7.794</v>
+        <v>7.081</v>
       </c>
       <c r="H24" t="n">
         <v>7.081</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0435</v>
+        <v>0.0345</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0568</v>
+        <v>0.0459</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0261</v>
+        <v>0.0222</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0.1333</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2598</v>
+        <v>0.236</v>
       </c>
       <c r="O24" t="n">
         <v>0.236</v>
@@ -3145,37 +3416,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.533</v>
+        <v>0.487</v>
       </c>
       <c r="C25" t="n">
-        <v>1.504</v>
+        <v>1.38</v>
       </c>
       <c r="D25" t="n">
-        <v>0.71</v>
+        <v>0.676</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>3.283</v>
       </c>
       <c r="G25" t="n">
-        <v>6.03</v>
+        <v>5.826</v>
       </c>
       <c r="H25" t="n">
         <v>5.826</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0172</v>
+        <v>0.0157</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0485</v>
+        <v>0.0445</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0229</v>
+        <v>0.0218</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0.1059</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1945</v>
+        <v>0.1879</v>
       </c>
       <c r="O25" t="n">
         <v>0.1879</v>
@@ -3188,37 +3465,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.397</v>
+        <v>0.372</v>
       </c>
       <c r="C26" t="n">
-        <v>1.322</v>
+        <v>1.236</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.553</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>2.771</v>
       </c>
       <c r="G26" t="n">
-        <v>5.056</v>
+        <v>4.931</v>
       </c>
       <c r="H26" t="n">
         <v>4.931</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0128</v>
+        <v>0.012</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0426</v>
+        <v>0.0399</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0183</v>
+        <v>0.0178</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0.08939999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1631</v>
+        <v>0.1591</v>
       </c>
       <c r="O26" t="n">
         <v>0.1591</v>
@@ -3231,37 +3514,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="C27" t="n">
-        <v>1.193</v>
+        <v>1.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.672</v>
+        <v>0.679</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>1.569</v>
       </c>
       <c r="G27" t="n">
-        <v>3.779</v>
+        <v>3.797</v>
       </c>
       <c r="H27" t="n">
         <v>3.797</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0426</v>
+        <v>0.0429</v>
       </c>
       <c r="K27" t="n">
-        <v>0.024</v>
+        <v>0.0243</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0.056</v>
       </c>
       <c r="N27" t="n">
-        <v>0.135</v>
+        <v>0.1356</v>
       </c>
       <c r="O27" t="n">
         <v>0.1356</v>
@@ -3274,37 +3563,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.436</v>
+        <v>0.454</v>
       </c>
       <c r="C28" t="n">
-        <v>1.536</v>
+        <v>1.6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.012</v>
+        <v>1.037</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>2.257</v>
       </c>
       <c r="G28" t="n">
-        <v>5.241</v>
+        <v>5.348</v>
       </c>
       <c r="H28" t="n">
         <v>5.348</v>
       </c>
       <c r="I28" t="n">
-        <v>0.014</v>
+        <v>0.0146</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0496</v>
+        <v>0.0516</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0326</v>
+        <v>0.0335</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0.0728</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1691</v>
+        <v>0.1725</v>
       </c>
       <c r="O28" t="n">
         <v>0.1725</v>
@@ -3317,37 +3612,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.647</v>
+        <v>0.663</v>
       </c>
       <c r="C29" t="n">
-        <v>1.668</v>
+        <v>1.709</v>
       </c>
       <c r="D29" t="n">
-        <v>0.965</v>
+        <v>1.004</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>2.846</v>
       </c>
       <c r="G29" t="n">
-        <v>6.126</v>
+        <v>6.222</v>
       </c>
       <c r="H29" t="n">
         <v>6.222</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0216</v>
+        <v>0.0221</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0556</v>
+        <v>0.057</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0322</v>
+        <v>0.0335</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0.0949</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2042</v>
+        <v>0.2074</v>
       </c>
       <c r="O29" t="n">
         <v>0.2074</v>
@@ -3360,37 +3661,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.186</v>
+        <v>1.565</v>
       </c>
       <c r="C30" t="n">
-        <v>1.758</v>
+        <v>2.253</v>
       </c>
       <c r="D30" t="n">
-        <v>0.582</v>
+        <v>0.716</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>2.622</v>
       </c>
       <c r="G30" t="n">
-        <v>6.148</v>
+        <v>7.155</v>
       </c>
       <c r="H30" t="n">
         <v>7.155</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0383</v>
+        <v>0.0505</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0567</v>
+        <v>0.0727</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0188</v>
+        <v>0.0231</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0.08459999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1983</v>
+        <v>0.2308</v>
       </c>
       <c r="O30" t="n">
         <v>0.2308</v>
@@ -3403,37 +3710,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.118</v>
+        <v>3.537</v>
       </c>
       <c r="C31" t="n">
-        <v>2.389</v>
+        <v>2.668</v>
       </c>
       <c r="D31" t="n">
-        <v>0.611</v>
+        <v>0.673</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>3.257</v>
       </c>
       <c r="G31" t="n">
-        <v>9.375</v>
+        <v>10.135</v>
       </c>
       <c r="H31" t="n">
         <v>10.135</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1039</v>
+        <v>0.1179</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0796</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0204</v>
+        <v>0.0224</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0.1086</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3125</v>
+        <v>0.3378</v>
       </c>
       <c r="O31" t="n">
         <v>0.3378</v>
@@ -3446,37 +3759,43 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.811</v>
+        <v>4.179</v>
       </c>
       <c r="C32" t="n">
-        <v>2.132</v>
+        <v>2.322</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.607</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>3.41</v>
       </c>
       <c r="G32" t="n">
-        <v>9.912000000000001</v>
+        <v>10.519</v>
       </c>
       <c r="H32" t="n">
         <v>10.519</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1229</v>
+        <v>0.1348</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0688</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.018</v>
+        <v>0.0196</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0.11</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3197</v>
+        <v>0.3393</v>
       </c>
       <c r="O32" t="n">
         <v>0.3393</v>
@@ -3489,37 +3808,43 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.92</v>
+        <v>4.035</v>
       </c>
       <c r="C33" t="n">
-        <v>2.232</v>
+        <v>2.277</v>
       </c>
       <c r="D33" t="n">
-        <v>0.658</v>
+        <v>0.67</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>2.975</v>
       </c>
       <c r="G33" t="n">
-        <v>9.785</v>
+        <v>9.958</v>
       </c>
       <c r="H33" t="n">
         <v>9.958</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1265</v>
+        <v>0.1302</v>
       </c>
       <c r="J33" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0212</v>
+        <v>0.0216</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0.096</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3156</v>
+        <v>0.3212</v>
       </c>
       <c r="O33" t="n">
         <v>0.3212</v>
@@ -3532,37 +3857,43 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.097</v>
+        <v>3.665</v>
       </c>
       <c r="C34" t="n">
-        <v>2.165</v>
+        <v>1.969</v>
       </c>
       <c r="D34" t="n">
-        <v>0.706</v>
+        <v>0.664</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>1.518</v>
       </c>
       <c r="G34" t="n">
-        <v>8.486000000000001</v>
+        <v>7.815</v>
       </c>
       <c r="H34" t="n">
         <v>7.815</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1366</v>
+        <v>0.1222</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0722</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0235</v>
+        <v>0.0221</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0.0506</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2829</v>
+        <v>0.2605</v>
       </c>
       <c r="O34" t="n">
         <v>0.2605</v>
@@ -3575,37 +3906,43 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.775</v>
+        <v>2.262</v>
       </c>
       <c r="C35" t="n">
-        <v>1.889</v>
+        <v>1.57</v>
       </c>
       <c r="D35" t="n">
-        <v>1.112</v>
+        <v>1.005</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0.988</v>
       </c>
       <c r="G35" t="n">
-        <v>6.763</v>
+        <v>5.825</v>
       </c>
       <c r="H35" t="n">
         <v>5.825</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0895</v>
+        <v>0.073</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0609</v>
+        <v>0.0506</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0359</v>
+        <v>0.0324</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0.0319</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2182</v>
+        <v>0.1879</v>
       </c>
       <c r="O35" t="n">
         <v>0.1879</v>
@@ -3618,37 +3955,43 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.496</v>
+        <v>1.225</v>
       </c>
       <c r="C36" t="n">
-        <v>1.815</v>
+        <v>1.508</v>
       </c>
       <c r="D36" t="n">
-        <v>1.068</v>
+        <v>0.96</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0.601</v>
       </c>
       <c r="G36" t="n">
-        <v>4.98</v>
+        <v>4.293</v>
       </c>
       <c r="H36" t="n">
         <v>4.293</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0499</v>
+        <v>0.0408</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0605</v>
+        <v>0.0503</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0356</v>
+        <v>0.032</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0.02</v>
       </c>
       <c r="N36" t="n">
-        <v>0.166</v>
+        <v>0.1431</v>
       </c>
       <c r="O36" t="n">
         <v>0.1431</v>
@@ -3661,31 +4004,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.579</v>
+        <v>0.571</v>
       </c>
       <c r="C37" t="n">
-        <v>1.54</v>
+        <v>1.515</v>
       </c>
       <c r="D37" t="n">
         <v>1.085</v>
       </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" t="n">
-        <v>3.204</v>
+        <v>3.172</v>
       </c>
       <c r="H37" t="n">
         <v>3.172</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0187</v>
+        <v>0.0184</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0497</v>
+        <v>0.0489</v>
       </c>
       <c r="K37" t="n">
         <v>0.035</v>
       </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" t="n">
-        <v>0.1034</v>
+        <v>0.1023</v>
       </c>
       <c r="O37" t="n">
         <v>0.1023</v>
@@ -3698,31 +4053,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.42</v>
+        <v>0.391</v>
       </c>
       <c r="C38" t="n">
-        <v>1.415</v>
+        <v>1.31</v>
       </c>
       <c r="D38" t="n">
-        <v>1.096</v>
+        <v>1.033</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93</v>
+        <v>2.734</v>
       </c>
       <c r="H38" t="n">
         <v>2.734</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0135</v>
+        <v>0.0126</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0456</v>
+        <v>0.0423</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0354</v>
+        <v>0.0333</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0945</v>
+        <v>0.0882</v>
       </c>
       <c r="O38" t="n">
         <v>0.0882</v>
@@ -3735,37 +4102,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.359</v>
+        <v>0.353</v>
       </c>
       <c r="C39" t="n">
-        <v>1.326</v>
+        <v>1.301</v>
       </c>
       <c r="D39" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.411</v>
+        <v>2.378</v>
       </c>
       <c r="H39" t="n">
         <v>2.378</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0124</v>
+        <v>0.0122</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0457</v>
+        <v>0.0449</v>
       </c>
       <c r="K39" t="n">
         <v>0.025</v>
       </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="O39" t="n">
         <v>0.082</v>
@@ -3778,37 +4151,43 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.372</v>
+        <v>0.461</v>
       </c>
       <c r="C40" t="n">
-        <v>1.247</v>
+        <v>1.536</v>
       </c>
       <c r="D40" t="n">
-        <v>0.832</v>
+        <v>1.005</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>1.465</v>
       </c>
       <c r="G40" t="n">
-        <v>3.917</v>
+        <v>4.467</v>
       </c>
       <c r="H40" t="n">
         <v>4.467</v>
       </c>
       <c r="I40" t="n">
-        <v>0.012</v>
+        <v>0.0149</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0402</v>
+        <v>0.0495</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0268</v>
+        <v>0.0324</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0.0473</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1263</v>
+        <v>0.1441</v>
       </c>
       <c r="O40" t="n">
         <v>0.1441</v>
@@ -3821,37 +4200,43 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.596</v>
+        <v>0.599</v>
       </c>
       <c r="C41" t="n">
-        <v>1.876</v>
+        <v>1.879</v>
       </c>
       <c r="D41" t="n">
-        <v>1.382</v>
+        <v>1.381</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>2.606</v>
       </c>
       <c r="G41" t="n">
-        <v>6.46</v>
+        <v>6.465</v>
       </c>
       <c r="H41" t="n">
         <v>6.465</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0199</v>
+        <v>0.02</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0625</v>
+        <v>0.0626</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0461</v>
+        <v>0.046</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0.08690000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2153</v>
+        <v>0.2155</v>
       </c>
       <c r="O41" t="n">
         <v>0.2155</v>
@@ -3864,37 +4249,43 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.183</v>
+        <v>3.037</v>
       </c>
       <c r="C42" t="n">
-        <v>2.302</v>
+        <v>3.111</v>
       </c>
       <c r="D42" t="n">
-        <v>0.882</v>
+        <v>1.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>4.575</v>
       </c>
       <c r="G42" t="n">
-        <v>9.942</v>
+        <v>11.784</v>
       </c>
       <c r="H42" t="n">
         <v>11.784</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0704</v>
+        <v>0.098</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0743</v>
+        <v>0.1004</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0284</v>
+        <v>0.0342</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0.1476</v>
       </c>
       <c r="N42" t="n">
-        <v>0.3207</v>
+        <v>0.3801</v>
       </c>
       <c r="O42" t="n">
         <v>0.3801</v>
@@ -3907,37 +4298,43 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.623</v>
+        <v>3.559</v>
       </c>
       <c r="C43" t="n">
-        <v>2.378</v>
+        <v>2.356</v>
       </c>
       <c r="D43" t="n">
-        <v>0.584</v>
+        <v>0.592</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>4.26</v>
       </c>
       <c r="G43" t="n">
-        <v>10.845</v>
+        <v>10.766</v>
       </c>
       <c r="H43" t="n">
         <v>10.766</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1208</v>
+        <v>0.1186</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0793</v>
+        <v>0.0785</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0195</v>
+        <v>0.0197</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0.142</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3615</v>
+        <v>0.3589</v>
       </c>
       <c r="O43" t="n">
         <v>0.3589</v>
@@ -3950,37 +4347,43 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.374</v>
+        <v>4.995</v>
       </c>
       <c r="C44" t="n">
-        <v>2.473</v>
+        <v>2.761</v>
       </c>
       <c r="D44" t="n">
-        <v>0.533</v>
+        <v>0.591</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>1.912</v>
       </c>
       <c r="G44" t="n">
-        <v>9.292</v>
+        <v>10.258</v>
       </c>
       <c r="H44" t="n">
         <v>10.258</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1411</v>
+        <v>0.1611</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0798</v>
+        <v>0.0891</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0172</v>
+        <v>0.0191</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0.0617</v>
       </c>
       <c r="N44" t="n">
-        <v>0.2998</v>
+        <v>0.3309</v>
       </c>
       <c r="O44" t="n">
         <v>0.3309</v>
@@ -3993,37 +4396,43 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4.561</v>
+        <v>4.597</v>
       </c>
       <c r="C45" t="n">
-        <v>2.313</v>
+        <v>2.329</v>
       </c>
       <c r="D45" t="n">
-        <v>0.496</v>
+        <v>0.505</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>2.142</v>
       </c>
       <c r="G45" t="n">
-        <v>9.512</v>
+        <v>9.573</v>
       </c>
       <c r="H45" t="n">
         <v>9.573</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1471</v>
+        <v>0.1483</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0746</v>
+        <v>0.0751</v>
       </c>
       <c r="K45" t="n">
-        <v>0.016</v>
+        <v>0.0163</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0.06909999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>0.3068</v>
+        <v>0.3088</v>
       </c>
       <c r="O45" t="n">
         <v>0.3088</v>
@@ -4036,37 +4445,43 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.94</v>
+        <v>2.89</v>
       </c>
       <c r="C46" t="n">
-        <v>2.203</v>
+        <v>1.673</v>
       </c>
       <c r="D46" t="n">
-        <v>0.92</v>
+        <v>0.761</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>2.163</v>
       </c>
       <c r="G46" t="n">
-        <v>9.225</v>
+        <v>7.487</v>
       </c>
       <c r="H46" t="n">
         <v>7.487</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1313</v>
+        <v>0.0963</v>
       </c>
       <c r="J46" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0558</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0307</v>
+        <v>0.0254</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0.0721</v>
       </c>
       <c r="N46" t="n">
-        <v>0.3075</v>
+        <v>0.2496</v>
       </c>
       <c r="O46" t="n">
         <v>0.2496</v>
@@ -4079,37 +4494,43 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.736</v>
+        <v>1.398</v>
       </c>
       <c r="C47" t="n">
-        <v>1.825</v>
+        <v>1.508</v>
       </c>
       <c r="D47" t="n">
-        <v>1.435</v>
+        <v>1.23</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>2.81</v>
       </c>
       <c r="G47" t="n">
-        <v>7.806</v>
+        <v>6.946</v>
       </c>
       <c r="H47" t="n">
         <v>6.946</v>
       </c>
       <c r="I47" t="n">
-        <v>0.056</v>
+        <v>0.0451</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0589</v>
+        <v>0.0486</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0463</v>
+        <v>0.0397</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0.0906</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2518</v>
+        <v>0.2241</v>
       </c>
       <c r="O47" t="n">
         <v>0.2241</v>
@@ -4122,37 +4543,43 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.742</v>
+        <v>0.66</v>
       </c>
       <c r="C48" t="n">
-        <v>1.598</v>
+        <v>1.427</v>
       </c>
       <c r="D48" t="n">
-        <v>1.165</v>
+        <v>1.085</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>1.827</v>
       </c>
       <c r="G48" t="n">
-        <v>5.333</v>
+        <v>4.999</v>
       </c>
       <c r="H48" t="n">
         <v>4.999</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0247</v>
+        <v>0.022</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0533</v>
+        <v>0.0476</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0388</v>
+        <v>0.0362</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0.0609</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1778</v>
+        <v>0.1666</v>
       </c>
       <c r="O48" t="n">
         <v>0.1666</v>
@@ -4165,37 +4592,43 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.509</v>
+        <v>0.511</v>
       </c>
       <c r="C49" t="n">
-        <v>1.478</v>
+        <v>1.481</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.955</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0.922</v>
       </c>
       <c r="G49" t="n">
-        <v>3.849</v>
+        <v>3.869</v>
       </c>
       <c r="H49" t="n">
         <v>3.869</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0477</v>
+        <v>0.0478</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0303</v>
+        <v>0.0308</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0.0297</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1241</v>
+        <v>0.1248</v>
       </c>
       <c r="O49" t="n">
         <v>0.1248</v>
@@ -4208,37 +4641,43 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.427</v>
+        <v>0.387</v>
       </c>
       <c r="C50" t="n">
-        <v>1.399</v>
+        <v>1.262</v>
       </c>
       <c r="D50" t="n">
-        <v>1.068</v>
+        <v>0.988</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0.573</v>
       </c>
       <c r="G50" t="n">
-        <v>3.467</v>
+        <v>3.211</v>
       </c>
       <c r="H50" t="n">
         <v>3.211</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0138</v>
+        <v>0.0125</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0451</v>
+        <v>0.0407</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0345</v>
+        <v>0.0319</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0.0185</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1118</v>
+        <v>0.1036</v>
       </c>
       <c r="O50" t="n">
         <v>0.1036</v>
@@ -4251,37 +4690,43 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.346</v>
+        <v>0.326</v>
       </c>
       <c r="C51" t="n">
-        <v>1.31</v>
+        <v>1.232</v>
       </c>
       <c r="D51" t="n">
-        <v>0.553</v>
+        <v>0.554</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>1.145</v>
       </c>
       <c r="G51" t="n">
-        <v>3.354</v>
+        <v>3.256</v>
       </c>
       <c r="H51" t="n">
         <v>3.256</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0124</v>
+        <v>0.0116</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0468</v>
+        <v>0.044</v>
       </c>
       <c r="K51" t="n">
         <v>0.0198</v>
       </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
       <c r="M51" t="n">
         <v>0.0409</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1198</v>
+        <v>0.1163</v>
       </c>
       <c r="O51" t="n">
         <v>0.1163</v>
@@ -4294,37 +4739,43 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.413</v>
+        <v>0.451</v>
       </c>
       <c r="C52" t="n">
-        <v>1.471</v>
+        <v>1.603</v>
       </c>
       <c r="D52" t="n">
-        <v>0.824</v>
+        <v>0.894</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>1.051</v>
       </c>
       <c r="G52" t="n">
-        <v>3.759</v>
+        <v>3.999</v>
       </c>
       <c r="H52" t="n">
         <v>3.999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0133</v>
+        <v>0.0145</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0474</v>
+        <v>0.0517</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0266</v>
+        <v>0.0288</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0.0339</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1212</v>
+        <v>0.129</v>
       </c>
       <c r="O52" t="n">
         <v>0.129</v>
@@ -4337,37 +4788,43 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.531</v>
+        <v>0.585</v>
       </c>
       <c r="C53" t="n">
-        <v>1.568</v>
+        <v>1.723</v>
       </c>
       <c r="D53" t="n">
-        <v>0.854</v>
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1.42</v>
       </c>
       <c r="G53" t="n">
-        <v>4.372</v>
+        <v>4.67</v>
       </c>
       <c r="H53" t="n">
         <v>4.67</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0177</v>
+        <v>0.0195</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0523</v>
+        <v>0.0574</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0285</v>
+        <v>0.0314</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0.0473</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1457</v>
+        <v>0.1557</v>
       </c>
       <c r="O53" t="n">
         <v>0.1557</v>
@@ -4380,37 +4837,43 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.132</v>
+        <v>1.436</v>
       </c>
       <c r="C54" t="n">
-        <v>2.025</v>
+        <v>2.515</v>
       </c>
       <c r="D54" t="n">
-        <v>0.864</v>
+        <v>0.995</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>2.585</v>
       </c>
       <c r="G54" t="n">
-        <v>6.606</v>
+        <v>7.532</v>
       </c>
       <c r="H54" t="n">
         <v>7.532</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0365</v>
+        <v>0.0463</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0653</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0279</v>
+        <v>0.0321</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.0834</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2131</v>
+        <v>0.243</v>
       </c>
       <c r="O54" t="n">
         <v>0.243</v>
@@ -4423,37 +4886,43 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.317</v>
+        <v>4.168</v>
       </c>
       <c r="C55" t="n">
-        <v>2.36</v>
+        <v>2.907</v>
       </c>
       <c r="D55" t="n">
-        <v>1.033</v>
+        <v>1.219</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>2.851</v>
       </c>
       <c r="G55" t="n">
-        <v>9.561999999999999</v>
+        <v>11.145</v>
       </c>
       <c r="H55" t="n">
         <v>11.145</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1106</v>
+        <v>0.1389</v>
       </c>
       <c r="J55" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0969</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0344</v>
+        <v>0.0406</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.095</v>
       </c>
       <c r="N55" t="n">
-        <v>0.3187</v>
+        <v>0.3715</v>
       </c>
       <c r="O55" t="n">
         <v>0.3715</v>
@@ -4466,37 +4935,43 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.837</v>
+        <v>4.988</v>
       </c>
       <c r="C56" t="n">
-        <v>2.515</v>
+        <v>2.557</v>
       </c>
       <c r="D56" t="n">
-        <v>1.057</v>
+        <v>1.065</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>3.825</v>
       </c>
       <c r="G56" t="n">
-        <v>12.234</v>
+        <v>12.434</v>
       </c>
       <c r="H56" t="n">
         <v>12.434</v>
       </c>
       <c r="I56" t="n">
-        <v>0.156</v>
+        <v>0.1609</v>
       </c>
       <c r="J56" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0825</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0341</v>
+        <v>0.0344</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.1234</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3947</v>
+        <v>0.4011</v>
       </c>
       <c r="O56" t="n">
         <v>0.4011</v>
@@ -4509,13 +4984,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.377</v>
+        <v>4.048</v>
       </c>
       <c r="C57" t="n">
-        <v>2.41</v>
+        <v>2.252</v>
       </c>
       <c r="D57" t="n">
-        <v>1.032</v>
+        <v>0.978</v>
       </c>
       <c r="E57" t="n">
         <v>0.001</v>
@@ -4524,19 +4999,19 @@
         <v>2.663</v>
       </c>
       <c r="G57" t="n">
-        <v>10.483</v>
+        <v>9.942</v>
       </c>
       <c r="H57" t="n">
         <v>9.942</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1412</v>
+        <v>0.1306</v>
       </c>
       <c r="J57" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0333</v>
+        <v>0.0315</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4545,7 +5020,7 @@
         <v>0.0859</v>
       </c>
       <c r="N57" t="n">
-        <v>0.3382</v>
+        <v>0.3207</v>
       </c>
       <c r="O57" t="n">
         <v>0.3207</v>
@@ -4558,13 +5033,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.372</v>
+        <v>3.102</v>
       </c>
       <c r="C58" t="n">
-        <v>1.982</v>
+        <v>1.83</v>
       </c>
       <c r="D58" t="n">
-        <v>0.944</v>
+        <v>0.884</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -4573,19 +5048,19 @@
         <v>1.827</v>
       </c>
       <c r="G58" t="n">
-        <v>8.125999999999999</v>
+        <v>7.643</v>
       </c>
       <c r="H58" t="n">
         <v>7.643</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1124</v>
+        <v>0.1034</v>
       </c>
       <c r="J58" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0315</v>
+        <v>0.0295</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4594,7 +5069,7 @@
         <v>0.0609</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2709</v>
+        <v>0.2548</v>
       </c>
       <c r="O58" t="n">
         <v>0.2548</v>
@@ -4607,13 +5082,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.91</v>
+        <v>1.453</v>
       </c>
       <c r="C59" t="n">
-        <v>2.052</v>
+        <v>1.617</v>
       </c>
       <c r="D59" t="n">
-        <v>1.007</v>
+        <v>0.844</v>
       </c>
       <c r="E59" t="n">
         <v>0.028</v>
@@ -4622,19 +5097,19 @@
         <v>3.326</v>
       </c>
       <c r="G59" t="n">
-        <v>8.321999999999999</v>
+        <v>7.268</v>
       </c>
       <c r="H59" t="n">
         <v>7.268</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0616</v>
+        <v>0.0469</v>
       </c>
       <c r="J59" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0522</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0325</v>
+        <v>0.0272</v>
       </c>
       <c r="L59" t="n">
         <v>0.0009</v>
@@ -4643,7 +5118,7 @@
         <v>0.1073</v>
       </c>
       <c r="N59" t="n">
-        <v>0.2685</v>
+        <v>0.2344</v>
       </c>
       <c r="O59" t="n">
         <v>0.2344</v>
@@ -4656,13 +5131,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.013</v>
+        <v>0.883</v>
       </c>
       <c r="C60" t="n">
-        <v>1.847</v>
+        <v>1.629</v>
       </c>
       <c r="D60" t="n">
-        <v>1.138</v>
+        <v>1.048</v>
       </c>
       <c r="E60" t="n">
         <v>0.039</v>
@@ -4671,19 +5146,19 @@
         <v>2.677</v>
       </c>
       <c r="G60" t="n">
-        <v>6.714</v>
+        <v>6.277</v>
       </c>
       <c r="H60" t="n">
         <v>6.277</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0338</v>
+        <v>0.0294</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0616</v>
+        <v>0.0543</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0379</v>
+        <v>0.0349</v>
       </c>
       <c r="L60" t="n">
         <v>0.0013</v>
@@ -4692,7 +5167,7 @@
         <v>0.0892</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2238</v>
+        <v>0.2092</v>
       </c>
       <c r="O60" t="n">
         <v>0.2092</v>
@@ -4705,13 +5180,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.485</v>
+        <v>0.459</v>
       </c>
       <c r="C61" t="n">
-        <v>1.48</v>
+        <v>1.395</v>
       </c>
       <c r="D61" t="n">
-        <v>1.232</v>
+        <v>1.179</v>
       </c>
       <c r="E61" t="n">
         <v>9.067</v>
@@ -4720,19 +5195,19 @@
         <v>2.003</v>
       </c>
       <c r="G61" t="n">
-        <v>14.267</v>
+        <v>14.102</v>
       </c>
       <c r="H61" t="n">
         <v>14.102</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0157</v>
+        <v>0.0148</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0477</v>
+        <v>0.045</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0397</v>
+        <v>0.038</v>
       </c>
       <c r="L61" t="n">
         <v>0.2925</v>
@@ -4741,7 +5216,7 @@
         <v>0.0646</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4602</v>
+        <v>0.4549</v>
       </c>
       <c r="O61" t="n">
         <v>0.4549</v>
@@ -4754,13 +5229,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.413</v>
+        <v>0.407</v>
       </c>
       <c r="C62" t="n">
-        <v>1.481</v>
+        <v>1.453</v>
       </c>
       <c r="D62" t="n">
-        <v>0.979</v>
+        <v>0.977</v>
       </c>
       <c r="E62" t="n">
         <v>8.375</v>
@@ -4769,19 +5244,19 @@
         <v>1.748</v>
       </c>
       <c r="G62" t="n">
-        <v>12.997</v>
+        <v>12.96</v>
       </c>
       <c r="H62" t="n">
         <v>12.96</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0133</v>
+        <v>0.0131</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0478</v>
+        <v>0.0469</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0316</v>
+        <v>0.0315</v>
       </c>
       <c r="L62" t="n">
         <v>0.2702</v>
@@ -4790,7 +5265,7 @@
         <v>0.0564</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4192</v>
+        <v>0.4181</v>
       </c>
       <c r="O62" t="n">
         <v>0.4181</v>
@@ -4803,13 +5278,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.425</v>
+        <v>0.36</v>
       </c>
       <c r="C63" t="n">
-        <v>1.413</v>
+        <v>1.208</v>
       </c>
       <c r="D63" t="n">
-        <v>1.136</v>
+        <v>0.989</v>
       </c>
       <c r="E63" t="n">
         <v>14.845</v>
@@ -4818,19 +5293,19 @@
         <v>1.847</v>
       </c>
       <c r="G63" t="n">
-        <v>19.666</v>
+        <v>19.249</v>
       </c>
       <c r="H63" t="n">
         <v>19.249</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0152</v>
+        <v>0.0129</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0505</v>
+        <v>0.0431</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0406</v>
+        <v>0.0353</v>
       </c>
       <c r="L63" t="n">
         <v>0.5302</v>
@@ -4839,7 +5314,7 @@
         <v>0.066</v>
       </c>
       <c r="N63" t="n">
-        <v>0.7024</v>
+        <v>0.6875</v>
       </c>
       <c r="O63" t="n">
         <v>0.6875</v>
@@ -4852,13 +5327,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.319</v>
+        <v>0.352</v>
       </c>
       <c r="C64" t="n">
-        <v>1.621</v>
+        <v>1.795</v>
       </c>
       <c r="D64" t="n">
-        <v>0.995</v>
+        <v>1.096</v>
       </c>
       <c r="E64" t="n">
         <v>23.016</v>
@@ -4867,19 +5342,19 @@
         <v>3.099</v>
       </c>
       <c r="G64" t="n">
-        <v>29.051</v>
+        <v>29.359</v>
       </c>
       <c r="H64" t="n">
         <v>29.359</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0103</v>
+        <v>0.0114</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0523</v>
+        <v>0.0579</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0321</v>
+        <v>0.0354</v>
       </c>
       <c r="L64" t="n">
         <v>0.7425</v>
@@ -4888,7 +5363,7 @@
         <v>0.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0.9371</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="O64" t="n">
         <v>0.9471000000000001</v>
@@ -4901,13 +5376,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.572</v>
+        <v>0.596</v>
       </c>
       <c r="C65" t="n">
-        <v>1.796</v>
+        <v>1.863</v>
       </c>
       <c r="D65" t="n">
-        <v>1.235</v>
+        <v>1.27</v>
       </c>
       <c r="E65" t="n">
         <v>6.972</v>
@@ -4916,19 +5391,19 @@
         <v>2.312</v>
       </c>
       <c r="G65" t="n">
-        <v>12.885</v>
+        <v>13.012</v>
       </c>
       <c r="H65" t="n">
         <v>13.012</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0191</v>
+        <v>0.0199</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0599</v>
+        <v>0.0621</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0412</v>
+        <v>0.0423</v>
       </c>
       <c r="L65" t="n">
         <v>0.2324</v>
@@ -4937,7 +5412,7 @@
         <v>0.0771</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4295</v>
+        <v>0.4337</v>
       </c>
       <c r="O65" t="n">
         <v>0.4337</v>
@@ -4950,13 +5425,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.961</v>
+        <v>2.713</v>
       </c>
       <c r="C66" t="n">
-        <v>2.536</v>
+        <v>3.431</v>
       </c>
       <c r="D66" t="n">
-        <v>1.402</v>
+        <v>1.729</v>
       </c>
       <c r="E66" t="n">
         <v>0.284</v>
@@ -4965,19 +5440,19 @@
         <v>1.549</v>
       </c>
       <c r="G66" t="n">
-        <v>7.731</v>
+        <v>9.706</v>
       </c>
       <c r="H66" t="n">
         <v>9.706</v>
       </c>
       <c r="I66" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0818</v>
+        <v>0.1107</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0452</v>
+        <v>0.0558</v>
       </c>
       <c r="L66" t="n">
         <v>0.0092</v>
@@ -4986,7 +5461,7 @@
         <v>0.05</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2494</v>
+        <v>0.3131</v>
       </c>
       <c r="O66" t="n">
         <v>0.3131</v>
@@ -4999,13 +5474,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.955</v>
+        <v>4.299</v>
       </c>
       <c r="C67" t="n">
-        <v>2.595</v>
+        <v>2.762</v>
       </c>
       <c r="D67" t="n">
-        <v>1.551</v>
+        <v>1.623</v>
       </c>
       <c r="E67" t="n">
         <v>2.178</v>
@@ -5014,19 +5489,19 @@
         <v>2.378</v>
       </c>
       <c r="G67" t="n">
-        <v>12.658</v>
+        <v>13.24</v>
       </c>
       <c r="H67" t="n">
         <v>13.24</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1318</v>
+        <v>0.1433</v>
       </c>
       <c r="J67" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0921</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0517</v>
+        <v>0.0541</v>
       </c>
       <c r="L67" t="n">
         <v>0.0726</v>
@@ -5035,7 +5510,7 @@
         <v>0.0793</v>
       </c>
       <c r="N67" t="n">
-        <v>0.4219</v>
+        <v>0.4413</v>
       </c>
       <c r="O67" t="n">
         <v>0.4413</v>
@@ -8677,7 +9152,7 @@
         <v>1548622</v>
       </c>
       <c r="H66" t="n">
-        <v>340068.0687041668</v>
+        <v>340068.0687041669</v>
       </c>
       <c r="I66" t="n">
         <v>283862</v>
@@ -8707,7 +9182,7 @@
         <v>1440406.018332258</v>
       </c>
       <c r="R66" t="n">
-        <v>493804.658415446</v>
+        <v>493804.6584154461</v>
       </c>
     </row>
     <row r="67">

--- a/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
@@ -61,9 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -158,6 +159,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -314,11 +316,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -346,6 +360,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -360,6 +375,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -871,7 +887,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -891,7 +907,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -911,7 +927,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -931,7 +947,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -951,7 +967,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -971,7 +987,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -991,7 +1007,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1011,7 +1027,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1031,7 +1047,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1051,7 +1067,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1071,7 +1087,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1091,7 +1107,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1111,7 +1127,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1131,7 +1147,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1151,7 +1167,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1171,7 +1187,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1191,7 +1207,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1211,7 +1227,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1231,7 +1247,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1251,7 +1267,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1271,7 +1287,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1291,7 +1307,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1311,7 +1327,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1331,7 +1347,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1351,7 +1367,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1371,7 +1387,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1391,7 +1407,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1411,7 +1427,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1431,7 +1447,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1451,7 +1467,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1471,7 +1487,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1491,7 +1507,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1511,7 +1527,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1531,7 +1547,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1551,7 +1567,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1571,7 +1587,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1591,7 +1607,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1611,7 +1627,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1631,7 +1647,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1651,7 +1667,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1671,7 +1687,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1691,7 +1707,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1711,7 +1727,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1731,7 +1747,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1751,7 +1767,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1771,7 +1787,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1791,7 +1807,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1811,7 +1827,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1831,7 +1847,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1851,7 +1867,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1871,7 +1887,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1891,7 +1907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1911,7 +1927,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1931,7 +1947,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1951,7 +1967,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -1971,7 +1987,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -1991,7 +2007,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2011,7 +2027,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2031,7 +2047,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2051,7 +2067,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2071,7 +2087,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2091,7 +2107,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2111,7 +2127,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2131,7 +2147,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2151,7 +2167,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2171,7 +2187,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">

--- a/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/uruguay_gas_demand_by_sector.xlsx
@@ -154,7 +154,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Uruguay gas demand by sector (to Jun/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Uruguay gas demand by sector (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -184,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$67</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$67</f>
+              <f>'Chart'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -212,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$67</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$67</f>
+              <f>'Chart'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$67</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$67</f>
+              <f>'Chart'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -268,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$67</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$67</f>
+              <f>'Chart'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -296,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$67</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$67</f>
+              <f>'Chart'!$F$2:$F$68</f>
             </numRef>
           </val>
         </ser>
@@ -848,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2191,19 +2192,39 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1433</v>
+        <v>0.1439</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0921</v>
+        <v>0.0907</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0541</v>
+        <v>0.0549</v>
       </c>
       <c r="E67" t="n">
         <v>0.0726</v>
       </c>
       <c r="F67" t="n">
         <v>0.0793</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.097</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,13 +5511,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.299</v>
+        <v>4.316</v>
       </c>
       <c r="C67" t="n">
-        <v>2.762</v>
+        <v>2.721</v>
       </c>
       <c r="D67" t="n">
-        <v>1.623</v>
+        <v>1.646</v>
       </c>
       <c r="E67" t="n">
         <v>2.178</v>
@@ -5511,13 +5532,13 @@
         <v>13.24</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1433</v>
+        <v>0.1439</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0921</v>
+        <v>0.0907</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0541</v>
+        <v>0.0549</v>
       </c>
       <c r="L67" t="n">
         <v>0.0726</v>
@@ -5530,6 +5551,55 @@
       </c>
       <c r="O67" t="n">
         <v>0.4413</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4.699</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="G68" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="H68" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.4112</v>
       </c>
     </row>
   </sheetData>
@@ -5543,7 +5613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9247,7 +9317,7 @@
         <v>133835</v>
       </c>
       <c r="O67" t="n">
-        <v>536541</v>
+        <v>468051</v>
       </c>
       <c r="P67" t="n">
         <v>9474537</v>
@@ -9257,6 +9327,61 @@
       </c>
       <c r="R67" t="n">
         <v>337982.1036615145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>160904.6563198857</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1239916</v>
+      </c>
+      <c r="D68" t="n">
+        <v>560053</v>
+      </c>
+      <c r="E68" t="n">
+        <v>397696</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6981076</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3008095</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1356163</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4613653.053936</v>
+      </c>
+      <c r="K68" t="n">
+        <v>23378</v>
+      </c>
+      <c r="L68" t="n">
+        <v>384914</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2308555</v>
+      </c>
+      <c r="N68" t="n">
+        <v>162481</v>
+      </c>
+      <c r="O68" t="n">
+        <v>493505</v>
+      </c>
+      <c r="P68" t="n">
+        <v>9989171</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2596079</v>
+      </c>
+      <c r="R68" t="n">
+        <v>160904.6563198857</v>
       </c>
     </row>
   </sheetData>
